--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -761,9 +761,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -1149,9 +1146,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1293,9 +1287,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1437,9 +1428,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1581,9 +1569,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1725,9 +1710,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1869,9 +1851,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2013,9 +1992,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2157,9 +2133,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2301,9 +2274,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2415,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2589,9 +2556,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2733,9 +2697,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2877,9 +2838,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3265,9 +3223,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3409,9 +3364,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3553,9 +3505,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3697,9 +3646,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3841,9 +3787,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -3985,9 +3928,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -4129,9 +4069,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -4273,9 +4210,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4417,9 +4351,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -4561,9 +4492,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -4705,9 +4633,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -4849,9 +4774,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -4993,9 +4915,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5381,9 +5300,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -5525,9 +5441,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -5669,9 +5582,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -5813,9 +5723,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -5957,9 +5864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -6101,9 +6005,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6245,9 +6146,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6389,9 +6287,6 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
@@ -6533,9 +6428,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -6677,9 +6569,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -6821,9 +6710,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -6965,9 +6851,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7109,9 +6992,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7497,9 +7377,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7641,9 +7518,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -7785,9 +7659,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -7929,9 +7800,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8073,9 +7941,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8217,9 +8082,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -8505,9 +8367,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -8793,9 +8652,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9081,9 +8937,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9369,9 +9222,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9657,9 +9507,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -9945,9 +9792,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10233,9 +10077,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -10621,9 +10462,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -10909,9 +10747,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11197,9 +11032,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11485,9 +11317,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -11773,9 +11602,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12061,9 +11887,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -12349,9 +12172,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -12637,9 +12457,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -12925,9 +12742,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -13213,9 +13027,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13501,9 +13312,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -13787,9 +13595,6 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">

--- a/diseases/d064/2005-2009.xlsx
+++ b/diseases/d064/2005-2009.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT2" t="n">
@@ -809,42 +809,42 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -918,22 +918,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_HISTORY</t>
+          <t>SRC_CA_PHAC_CNDSS</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Bólusótt</t>
+          <t>Smallpox</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>national_registry_notifications</t>
+          <t>provincial_territorial_voluntary_notifications_national</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:CA:national</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>historical</t>
+          <t>active</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>IS_DOH_historical_registry_annual</t>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
         </is>
       </c>
       <c r="AT3" t="n">
@@ -1039,42 +1039,42 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1154,68 +1154,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1242,17 +1256,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1273,12 +1287,12 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2005-02-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2005-02</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1287,76 +1301,165 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1517,12 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2005-03-01</t>
+          <t>2005-01-01</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2005-03</t>
+          <t>2005-01</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1555,12 +1658,12 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2005-04-01</t>
+          <t>2005-02-01</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2005-04</t>
+          <t>2005-02</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1696,12 +1799,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2005-05-01</t>
+          <t>2005-03-01</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2005-05</t>
+          <t>2005-03</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1837,12 +1940,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2005-06-01</t>
+          <t>2005-04-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2005-06</t>
+          <t>2005-04</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1978,12 +2081,12 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2005-07-01</t>
+          <t>2005-05-01</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2005-07</t>
+          <t>2005-05</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2119,12 +2222,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2005-08-01</t>
+          <t>2005-06-01</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2005-08</t>
+          <t>2005-06</t>
         </is>
       </c>
       <c r="N11" t="n">
@@ -2260,12 +2363,12 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2005-09-01</t>
+          <t>2005-07-01</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2005-09</t>
+          <t>2005-07</t>
         </is>
       </c>
       <c r="N12" t="n">
@@ -2401,12 +2504,12 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2005-10-01</t>
+          <t>2005-08-01</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2005-10</t>
+          <t>2005-08</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2542,12 +2645,12 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2005-11-01</t>
+          <t>2005-09-01</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2005-11</t>
+          <t>2005-09</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2683,12 +2786,12 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2005-12-01</t>
+          <t>2005-10-01</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2005-12</t>
+          <t>2005-10</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -2798,12 +2901,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2824,12 +2927,12 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-11-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-11</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -2846,82 +2949,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -2948,17 +3037,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2979,12 +3068,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2005-12-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2006-01</t>
+          <t>2005-12</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -2993,165 +3082,76 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN17" t="b">
-        <v>1</v>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3231,68 +3231,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3319,17 +3333,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3350,12 +3364,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2006-02-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2006-02</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3364,76 +3378,165 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3568,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3491,12 +3594,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2006-03-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2006-03</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -3513,68 +3616,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3601,17 +3718,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3632,12 +3749,12 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2006-04-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2006-04</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N21" t="n">
@@ -3646,76 +3763,165 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3979,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2006-05-01</t>
+          <t>2006-01-01</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2006-05</t>
+          <t>2006-01</t>
         </is>
       </c>
       <c r="N22" t="n">
@@ -3914,12 +4120,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2006-06-01</t>
+          <t>2006-02-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2006-06</t>
+          <t>2006-02</t>
         </is>
       </c>
       <c r="N23" t="n">
@@ -4055,12 +4261,12 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2006-07-01</t>
+          <t>2006-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2006-07</t>
+          <t>2006-03</t>
         </is>
       </c>
       <c r="N24" t="n">
@@ -4196,12 +4402,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2006-08-01</t>
+          <t>2006-04-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2006-08</t>
+          <t>2006-04</t>
         </is>
       </c>
       <c r="N25" t="n">
@@ -4337,12 +4543,12 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2006-09-01</t>
+          <t>2006-05-01</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2006-09</t>
+          <t>2006-05</t>
         </is>
       </c>
       <c r="N26" t="n">
@@ -4478,12 +4684,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2006-10-01</t>
+          <t>2006-06-01</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2006-10</t>
+          <t>2006-06</t>
         </is>
       </c>
       <c r="N27" t="n">
@@ -4619,12 +4825,12 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2006-11-01</t>
+          <t>2006-07-01</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2006-11</t>
+          <t>2006-07</t>
         </is>
       </c>
       <c r="N28" t="n">
@@ -4760,12 +4966,12 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2006-12-01</t>
+          <t>2006-08-01</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2006-12</t>
+          <t>2006-08</t>
         </is>
       </c>
       <c r="N29" t="n">
@@ -4875,12 +5081,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4901,12 +5107,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-09-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-09</t>
         </is>
       </c>
       <c r="N30" t="n">
@@ -4923,82 +5129,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5025,17 +5217,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5056,12 +5248,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-10-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-10</t>
         </is>
       </c>
       <c r="N31" t="n">
@@ -5070,165 +5262,76 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN31" t="b">
-        <v>1</v>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5389,12 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2006-11-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2007-01</t>
+          <t>2006-11</t>
         </is>
       </c>
       <c r="N32" t="n">
@@ -5427,12 +5530,12 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2007-02-01</t>
+          <t>2006-12-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2007-02</t>
+          <t>2006-12</t>
         </is>
       </c>
       <c r="N33" t="n">
@@ -5542,12 +5645,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5568,12 +5671,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2007-03-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2007-03</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N34" t="n">
@@ -5590,68 +5693,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5678,17 +5795,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -5709,12 +5826,12 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2007-04-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2007-04</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N35" t="n">
@@ -5723,76 +5840,165 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -5824,12 +6030,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5850,12 +6056,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2007-05-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2007-05</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N36" t="n">
@@ -5872,68 +6078,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -5960,17 +6180,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5991,12 +6211,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2007-06-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2007-06</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N37" t="n">
@@ -6005,76 +6225,165 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -6132,12 +6441,12 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2007-07-01</t>
+          <t>2007-01-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2007-07</t>
+          <t>2007-01</t>
         </is>
       </c>
       <c r="N38" t="n">
@@ -6273,12 +6582,12 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2007-08-01</t>
+          <t>2007-02-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2007-08</t>
+          <t>2007-02</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -6414,12 +6723,12 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2007-09-01</t>
+          <t>2007-03-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2007-09</t>
+          <t>2007-03</t>
         </is>
       </c>
       <c r="N40" t="n">
@@ -6555,12 +6864,12 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2007-10-01</t>
+          <t>2007-04-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2007-10</t>
+          <t>2007-04</t>
         </is>
       </c>
       <c r="N41" t="n">
@@ -6696,12 +7005,12 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
+          <t>2007-05-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2007-11</t>
+          <t>2007-05</t>
         </is>
       </c>
       <c r="N42" t="n">
@@ -6837,12 +7146,12 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2007-12-01</t>
+          <t>2007-06-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2007-12</t>
+          <t>2007-06</t>
         </is>
       </c>
       <c r="N43" t="n">
@@ -6952,12 +7261,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -6978,12 +7287,12 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-07-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-07</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7000,82 +7309,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS44" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7102,17 +7397,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7133,12 +7428,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-08-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-08</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7147,165 +7442,76 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN45" t="b">
-        <v>1</v>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS45" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7363,12 +7569,12 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2007-09-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2008-01</t>
+          <t>2007-09</t>
         </is>
       </c>
       <c r="N46" t="n">
@@ -7504,12 +7710,12 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2008-02-01</t>
+          <t>2007-10-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2008-02</t>
+          <t>2007-10</t>
         </is>
       </c>
       <c r="N47" t="n">
@@ -7645,12 +7851,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2008-03-01</t>
+          <t>2007-11-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2008-03</t>
+          <t>2007-11</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7786,12 +7992,12 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2008-04-01</t>
+          <t>2007-12-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2008-04</t>
+          <t>2007-12</t>
         </is>
       </c>
       <c r="N49" t="n">
@@ -7901,12 +8107,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -7927,12 +8133,12 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2008-05</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7949,68 +8155,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8037,17 +8257,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8068,12 +8288,12 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2008-06-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2008-06</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -8082,76 +8302,165 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8183,12 +8492,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8209,12 +8518,12 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8223,9 +8532,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -8234,68 +8540,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8322,17 +8642,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8353,12 +8673,12 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2008-07-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2008-07</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N53" t="n">
@@ -8367,76 +8687,165 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8877,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8494,21 +8903,18 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-01</t>
         </is>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
@@ -8545,42 +8951,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8638,12 +9044,12 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2008-08-01</t>
+          <t>2008-02-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2008-08</t>
+          <t>2008-02</t>
         </is>
       </c>
       <c r="N55" t="n">
@@ -8753,12 +9159,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -8779,21 +9185,18 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-03-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-03</t>
         </is>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
@@ -8830,42 +9233,42 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8923,12 +9326,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>2008-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2008-09</t>
+          <t>2008-04</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9038,12 +9441,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9064,21 +9467,18 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-05</t>
         </is>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
@@ -9115,42 +9515,42 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -9208,12 +9608,12 @@
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2008-10-01</t>
+          <t>2008-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2008-10</t>
+          <t>2008-06</t>
         </is>
       </c>
       <c r="N59" t="n">
@@ -9349,12 +9749,12 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9493,12 +9893,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2008-11-01</t>
+          <t>2008-07-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2008-11</t>
+          <t>2008-07</t>
         </is>
       </c>
       <c r="N61" t="n">
@@ -9634,12 +10034,12 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N62" t="n">
@@ -9778,12 +10178,12 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2008-12-01</t>
+          <t>2008-08-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2008-12</t>
+          <t>2008-08</t>
         </is>
       </c>
       <c r="N63" t="n">
@@ -9919,12 +10319,12 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N64" t="n">
@@ -10037,12 +10437,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10063,12 +10463,12 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-09</t>
         </is>
       </c>
       <c r="N65" t="n">
@@ -10085,82 +10485,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ65" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -10187,17 +10573,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10218,12 +10604,12 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N66" t="n">
@@ -10232,165 +10618,79 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_HISTORY</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Bólusótt</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>national_registry_notifications</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG66" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>historical</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>IS_DOH_historical_registry_annual</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN66" t="b">
-        <v>1</v>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ66" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10448,12 +10748,12 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2008-10-01</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2009-01</t>
+          <t>2008-10</t>
         </is>
       </c>
       <c r="N67" t="n">
@@ -10589,12 +10889,12 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N68" t="n">
@@ -10733,12 +11033,12 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2009-02-01</t>
+          <t>2008-11-01</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2009-02</t>
+          <t>2008-11</t>
         </is>
       </c>
       <c r="N69" t="n">
@@ -10874,12 +11174,12 @@
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N70" t="n">
@@ -11018,12 +11318,12 @@
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2009-03-01</t>
+          <t>2008-12-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2009-03</t>
+          <t>2008-12</t>
         </is>
       </c>
       <c r="N71" t="n">
@@ -11133,12 +11433,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -11159,12 +11459,12 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N72" t="n">
@@ -11173,9 +11473,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11184,68 +11481,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11272,17 +11583,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -11303,12 +11614,12 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2009-04-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2009-04</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N73" t="n">
@@ -11317,76 +11628,165 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D112_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11844,12 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N74" t="n">
@@ -11562,12 +11962,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -11588,12 +11988,12 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2009-05-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2009-05</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N75" t="n">
@@ -11610,68 +12010,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11698,17 +12112,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -11729,12 +12143,12 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N76" t="n">
@@ -11743,79 +12157,165 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_HISTORY</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Bólusótt</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>national_registry_notifications</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>historical</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>IS_DOH_historical_registry_annual</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Iceland historical national-registry annual notifications; published dashes mean not applicable and blank cells remain unknown.</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN76" t="b">
+        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>SER_IS_HISTORY_SMALLPOX_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -11873,12 +12373,12 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2009-06-01</t>
+          <t>2009-01-01</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2009-06</t>
+          <t>2009-01</t>
         </is>
       </c>
       <c r="N77" t="n">
@@ -12014,12 +12514,12 @@
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N78" t="n">
@@ -12158,12 +12658,12 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2009-07-01</t>
+          <t>2009-02-01</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2009-07</t>
+          <t>2009-02</t>
         </is>
       </c>
       <c r="N79" t="n">
@@ -12299,12 +12799,12 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N80" t="n">
@@ -12443,12 +12943,12 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2009-08-01</t>
+          <t>2009-03-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2009-08</t>
+          <t>2009-03</t>
         </is>
       </c>
       <c r="N81" t="n">
@@ -12584,12 +13084,12 @@
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N82" t="n">
@@ -12728,12 +13228,12 @@
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2009-09-01</t>
+          <t>2009-04-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2009-09</t>
+          <t>2009-04</t>
         </is>
       </c>
       <c r="N83" t="n">
@@ -12869,12 +13369,12 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N84" t="n">
@@ -13013,12 +13513,12 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2009-10-01</t>
+          <t>2009-05-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2009-10</t>
+          <t>2009-05</t>
         </is>
       </c>
       <c r="N85" t="n">
@@ -13154,12 +13654,12 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N86" t="n">
@@ -13298,12 +13798,12 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2009-11-01</t>
+          <t>2009-06-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2009-11</t>
+          <t>2009-06</t>
         </is>
       </c>
       <c r="N87" t="n">
@@ -13439,12 +13939,12 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N88" t="n">
@@ -13583,12 +14083,12 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2009-12-01</t>
+          <t>2009-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2009-12</t>
+          <t>2009-07</t>
         </is>
       </c>
       <c r="N89" t="n">
@@ -13665,6 +14165,1431 @@
         </is>
       </c>
       <c r="BC89" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
+      <c r="AT90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>2009-08-01</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>2009-08</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr"/>
+      <c r="AT91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr"/>
+      <c r="AT92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2009-09-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2009-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
+      <c r="AT94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2009-10-01</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2009-10</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
+      <c r="AT96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2009-11-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2009-11</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>chp_notifiable</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>smallpox</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D064</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Smallpox</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2009-12-01</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2009-12</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -13786,7 +15711,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -13796,7 +15721,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -13816,7 +15741,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -13826,7 +15751,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
